--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119811964</v>
       </c>
       <c r="B2" t="n">
-        <v>77867</v>
+        <v>77883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,337 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122645585</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91792</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra Småvattnet, Stora blåsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>461482</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7188627</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal, nyligen blädad grannaturskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122645541</v>
+      </c>
+      <c r="B4" t="n">
+        <v>88040</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Östra Småvattnet, Stora blåsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>461592</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7188814</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I gammal, nyligen blädad grannaturskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122645610</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99495</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Småvattnet, Stora blåsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>461520</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7188825</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I gammal, nyligen blädad grannaturskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122645585</v>
       </c>
       <c r="B3" t="n">
-        <v>91792</v>
+        <v>91793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645541</v>
+        <v>122645610</v>
       </c>
       <c r="B4" t="n">
-        <v>88040</v>
+        <v>99496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +903,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461592</v>
+        <v>461520</v>
       </c>
       <c r="R4" t="n">
-        <v>7188814</v>
+        <v>7188825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645610</v>
+        <v>122645541</v>
       </c>
       <c r="B5" t="n">
-        <v>99495</v>
+        <v>88041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2082</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461520</v>
+        <v>461592</v>
       </c>
       <c r="R5" t="n">
-        <v>7188825</v>
+        <v>7188814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645585</v>
+        <v>122645541</v>
       </c>
       <c r="B3" t="n">
-        <v>91793</v>
+        <v>88044</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461482</v>
+        <v>461592</v>
       </c>
       <c r="R3" t="n">
-        <v>7188627</v>
+        <v>7188814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +894,7 @@
         <v>122645610</v>
       </c>
       <c r="B4" t="n">
-        <v>99496</v>
+        <v>99499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645541</v>
+        <v>122645585</v>
       </c>
       <c r="B5" t="n">
-        <v>88041</v>
+        <v>91796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>4787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461592</v>
+        <v>461482</v>
       </c>
       <c r="R5" t="n">
-        <v>7188814</v>
+        <v>7188627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645541</v>
+        <v>122645585</v>
       </c>
       <c r="B3" t="n">
-        <v>88044</v>
+        <v>91796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4412</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461592</v>
+        <v>461482</v>
       </c>
       <c r="R3" t="n">
-        <v>7188814</v>
+        <v>7188627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645585</v>
+        <v>122645541</v>
       </c>
       <c r="B5" t="n">
-        <v>91796</v>
+        <v>88044</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4787</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461482</v>
+        <v>461592</v>
       </c>
       <c r="R5" t="n">
-        <v>7188627</v>
+        <v>7188814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645585</v>
+        <v>122645541</v>
       </c>
       <c r="B3" t="n">
-        <v>91899</v>
+        <v>88151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>4412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461482</v>
+        <v>461592</v>
       </c>
       <c r="R3" t="n">
-        <v>7188627</v>
+        <v>7188814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +894,7 @@
         <v>122645610</v>
       </c>
       <c r="B4" t="n">
-        <v>99602</v>
+        <v>99610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645541</v>
+        <v>122645585</v>
       </c>
       <c r="B5" t="n">
-        <v>88147</v>
+        <v>91903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>4787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461592</v>
+        <v>461482</v>
       </c>
       <c r="R5" t="n">
-        <v>7188814</v>
+        <v>7188627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645541</v>
+        <v>122645585</v>
       </c>
       <c r="B3" t="n">
-        <v>88151</v>
+        <v>91903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4412</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461592</v>
+        <v>461482</v>
       </c>
       <c r="R3" t="n">
-        <v>7188814</v>
+        <v>7188627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645610</v>
+        <v>122645541</v>
       </c>
       <c r="B4" t="n">
-        <v>99610</v>
+        <v>88151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461520</v>
+        <v>461592</v>
       </c>
       <c r="R4" t="n">
-        <v>7188825</v>
+        <v>7188814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645585</v>
+        <v>122645610</v>
       </c>
       <c r="B5" t="n">
-        <v>91903</v>
+        <v>99610</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,26 +1017,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461482</v>
+        <v>461520</v>
       </c>
       <c r="R5" t="n">
-        <v>7188627</v>
+        <v>7188825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>122645610</v>
       </c>
       <c r="B5" t="n">
-        <v>99610</v>
+        <v>99612</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645541</v>
+        <v>122645610</v>
       </c>
       <c r="B4" t="n">
-        <v>88151</v>
+        <v>99612</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +903,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461592</v>
+        <v>461520</v>
       </c>
       <c r="R4" t="n">
-        <v>7188814</v>
+        <v>7188825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645610</v>
+        <v>122645541</v>
       </c>
       <c r="B5" t="n">
-        <v>99612</v>
+        <v>88151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1014,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2082</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461520</v>
+        <v>461592</v>
       </c>
       <c r="R5" t="n">
-        <v>7188825</v>
+        <v>7188814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645585</v>
+        <v>122645610</v>
       </c>
       <c r="B3" t="n">
-        <v>91903</v>
+        <v>99620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>2082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461482</v>
+        <v>461520</v>
       </c>
       <c r="R3" t="n">
-        <v>7188627</v>
+        <v>7188825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645610</v>
+        <v>122645585</v>
       </c>
       <c r="B4" t="n">
-        <v>99612</v>
+        <v>91911</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,27 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461520</v>
+        <v>461482</v>
       </c>
       <c r="R4" t="n">
-        <v>7188825</v>
+        <v>7188627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645585</v>
+        <v>122645541</v>
       </c>
       <c r="B4" t="n">
-        <v>91911</v>
+        <v>88151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4787</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461482</v>
+        <v>461592</v>
       </c>
       <c r="R4" t="n">
-        <v>7188627</v>
+        <v>7188814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645541</v>
+        <v>122645585</v>
       </c>
       <c r="B5" t="n">
-        <v>88151</v>
+        <v>91911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>4787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461592</v>
+        <v>461482</v>
       </c>
       <c r="R5" t="n">
-        <v>7188814</v>
+        <v>7188627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62886-2023 artfynd.xlsx
+++ b/artfynd/A 62886-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122645610</v>
+        <v>122645585</v>
       </c>
       <c r="B3" t="n">
-        <v>99620</v>
+        <v>91911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2082</v>
+        <v>4787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461520</v>
+        <v>461482</v>
       </c>
       <c r="R3" t="n">
-        <v>7188825</v>
+        <v>7188627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645541</v>
+        <v>122645610</v>
       </c>
       <c r="B4" t="n">
-        <v>88151</v>
+        <v>99620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +903,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461592</v>
+        <v>461520</v>
       </c>
       <c r="R4" t="n">
-        <v>7188814</v>
+        <v>7188825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645585</v>
+        <v>122645541</v>
       </c>
       <c r="B5" t="n">
-        <v>91911</v>
+        <v>88151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4787</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461482</v>
+        <v>461592</v>
       </c>
       <c r="R5" t="n">
-        <v>7188627</v>
+        <v>7188814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
